--- a/GameDesign/BOSS技能设计.xlsx
+++ b/GameDesign/BOSS技能设计.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator.DESKTOP-0DOPE9C\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\GameDesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF548F09-2262-4191-AB03-CC723BC7D881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD841C11-5C34-4A22-BEAA-4F3E9BB619F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
-  <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
   <si>
     <t>狂暴</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -332,10 +327,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>吟唱1秒，地脉领主在自身周围展开磁力领域，对附近单位造成300%伤害,并且使目标附加磁力效果，降低范围内敌人的10%移动速度和攻击速度，可叠加10层，持续8秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>核心磁力空间的叠加buff,考验玩家快速打断技能,然后还有巨石冲撞,考验玩家可以不依靠读条,看BOSS技能动作躲避的技能。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -378,6 +369,119 @@
   <si>
     <t>核心首先是让玩家要优先击杀恢复图腾，恢复图腾的血不是很多,摸几下就没了。然后考验玩家的数值是否过关,所以设计了自然之力和龙卷风暴永久存在的技能,时间一长,场面就会混乱</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cyan meteor hit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特效资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击特效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spear AoE(Clone)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Totem water(Clone)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire explosion(Clone)   1次爆炸 2次爆炸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock stride</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Violet arcane bust2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind Tornado</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnchantedGround_Fire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lava spikes(Clone)/FX_Explosion_O_1/Eff_Skill_BaoZhaQian_4(Clone)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HCFX_Energy_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire crossfade/FX_Explosion_H_1/HCFX_Meteor_03_Single</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_EarthSkill_Path_05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_EarthSkill_Energy_01 (改)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_splash_thorn_02_floo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_splash_thorn_01_floor(改绿)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electro throw+Fire throw/Fire Spray</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Orb_Fire</t>
+  </si>
+  <si>
+    <t>ConjureWaterPool</t>
+  </si>
+  <si>
+    <t>EnchantedGround_Fire/FX_Dust_Fire(改大小)/ConjureAmethystSea(改)/MeteorStrike(Clone)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StormPillar(Clone)+SummonStorm(Clone)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟1秒，地脉领主在自身周围展开磁力领域，对附近单位造成300%伤害,并且使目标附加磁力效果，降低范围内敌人的10%移动速度和攻击速度，可叠加10层，持续8秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BarrelOfConfusion_Static/FocusedExplosion_01_Delayed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shrapnel_01+Shrapnel_01_AltElements（需要箭头）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eff_Skill_ChiXu_15</t>
+  </si>
+  <si>
+    <t>Eff_Skill_ChongFeng(Clone)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Summon_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_BufHealStatus_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -558,9 +662,6 @@
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -585,6 +686,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -597,38 +731,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1174,468 +1278,621 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:G66"/>
+  <dimension ref="B1:I66"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="185.25" customWidth="1"/>
+    <col min="5" max="5" width="144.875" customWidth="1"/>
+    <col min="6" max="6" width="31.75" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="21"/>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="21"/>
+      <c r="C4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="11"/>
-      <c r="C3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="11"/>
-      <c r="C4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>18</v>
-      </c>
+      <c r="F4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="11"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="9"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="11"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="18" t="s">
+      <c r="B7" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20"/>
+      <c r="C7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="22"/>
+      <c r="C10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="12"/>
-      <c r="C10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="23"/>
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="23"/>
+      <c r="C12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="13"/>
-      <c r="C11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="13"/>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="24"/>
+      <c r="C13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="D13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="14"/>
-      <c r="C13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>29</v>
-      </c>
+      <c r="F13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="18"/>
+      <c r="C17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="19"/>
+      <c r="C18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="19"/>
+      <c r="C19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="20"/>
+      <c r="C20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="15"/>
-      <c r="C17" s="7" t="s">
+      <c r="F23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="18"/>
+      <c r="C24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="19"/>
+      <c r="C25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="19"/>
+      <c r="C26" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="20"/>
+      <c r="C27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="I27" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="18"/>
+      <c r="C31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="2:9" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="19"/>
+      <c r="C32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="19"/>
+      <c r="C33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="20"/>
+      <c r="C34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="18"/>
+      <c r="C38" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="19"/>
+      <c r="C39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="16"/>
-      <c r="C18" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="E39" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="19"/>
+      <c r="C40" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="16"/>
-      <c r="C19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="17"/>
-      <c r="C20" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20"/>
-    </row>
-    <row r="22" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="15"/>
-      <c r="C24" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="16"/>
-      <c r="C25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="16"/>
-      <c r="C26" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="17"/>
-      <c r="C27" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="18" t="s">
+      <c r="E40" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="20"/>
+      <c r="C41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="10"/>
+      <c r="C42" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="16"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="20"/>
-    </row>
-    <row r="29" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="15"/>
-      <c r="C31" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="16"/>
-      <c r="C32" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="16"/>
-      <c r="C33" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="17"/>
-      <c r="C34" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="19"/>
-      <c r="E35" s="20"/>
-    </row>
-    <row r="36" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="15"/>
-      <c r="C38" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="16"/>
-      <c r="C39" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="16"/>
-      <c r="C40" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="17"/>
-      <c r="C41" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="25"/>
-      <c r="C42" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D43" s="19"/>
-      <c r="E43" s="20"/>
-    </row>
-    <row r="44" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="2:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="46" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E46" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="2:7" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="49" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="50" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="51" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1656,6 +1913,11 @@
     <row r="66" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B31:B34"/>
     <mergeCell ref="C43:E43"/>
     <mergeCell ref="B38:B41"/>
     <mergeCell ref="C7:E7"/>
@@ -1663,13 +1925,8 @@
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B31:B34"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
